--- a/r4-core-main/StructureDefinition-at-core-location.xlsx
+++ b/r4-core-main/StructureDefinition-at-core-location.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1904" uniqueCount="384">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1904" uniqueCount="385">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T09:19:25+00:00</t>
+    <t>2026-10-13T06:32:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -963,6 +963,10 @@
   </si>
   <si>
     <t>If locations can be visited, we need to keep track of their address.</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+at-addr-1:If the extension for street name is used then the value for line must not be empty {line.all($this.extension('http://hl7.org/fhir/StructureDefinition/iso21090-ADXP-streetName').empty() or $this.hasValue())}at-addr-2:If the extension for street number is used then the value for line must not be empty {line.all($this.extension('http://hl7.org/fhir/StructureDefinition/iso21090-ADXP-houseNumber').empty() or $this.hasValue())}at-addr-3:If the extension for floor/door number is used then the value for line must not be empty {line.all($this.extension('http://hl7.org/fhir/StructureDefinition/iso21090-ADXP-additionalLocator').empty() or $this.hasValue())}</t>
   </si>
   <si>
     <t>.addr</t>
@@ -5333,10 +5337,10 @@
         <v>21</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>96</v>
+        <v>306</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>21</v>
@@ -5344,10 +5348,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5373,14 +5377,14 @@
         <v>179</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>21</v>
@@ -5405,13 +5409,13 @@
         <v>21</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>21</v>
@@ -5429,7 +5433,7 @@
         <v>21</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>76</v>
@@ -5444,7 +5448,7 @@
         <v>96</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>289</v>
@@ -5452,10 +5456,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5478,17 +5482,17 @@
         <v>21</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>21</v>
@@ -5537,7 +5541,7 @@
         <v>21</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>76</v>
@@ -5552,7 +5556,7 @@
         <v>96</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>21</v>
@@ -5560,10 +5564,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5666,10 +5670,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5774,14 +5778,14 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -5803,10 +5807,10 @@
         <v>130</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="N40" t="s" s="2">
         <v>133</v>
@@ -5861,7 +5865,7 @@
         <v>21</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>76</v>
@@ -5884,10 +5888,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5910,13 +5914,13 @@
         <v>21</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -5967,7 +5971,7 @@
         <v>21</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>84</v>
@@ -5982,7 +5986,7 @@
         <v>96</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>21</v>
@@ -5990,10 +5994,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6016,13 +6020,13 @@
         <v>21</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6073,7 +6077,7 @@
         <v>21</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>84</v>
@@ -6088,7 +6092,7 @@
         <v>96</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>21</v>
@@ -6096,10 +6100,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6122,13 +6126,13 @@
         <v>21</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6179,7 +6183,7 @@
         <v>21</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>76</v>
@@ -6194,7 +6198,7 @@
         <v>96</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>21</v>
@@ -6202,10 +6206,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6228,19 +6232,19 @@
         <v>85</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>21</v>
@@ -6289,7 +6293,7 @@
         <v>21</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>76</v>
@@ -6304,7 +6308,7 @@
         <v>96</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>21</v>
@@ -6312,10 +6316,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6338,17 +6342,17 @@
         <v>21</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>21</v>
@@ -6397,7 +6401,7 @@
         <v>21</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>76</v>
@@ -6412,7 +6416,7 @@
         <v>96</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>21</v>
@@ -6420,10 +6424,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6446,16 +6450,16 @@
         <v>21</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -6505,7 +6509,7 @@
         <v>21</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>76</v>
@@ -6520,7 +6524,7 @@
         <v>96</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>21</v>
@@ -6528,10 +6532,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6634,10 +6638,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6742,14 +6746,14 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -6771,10 +6775,10 @@
         <v>130</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="N49" t="s" s="2">
         <v>133</v>
@@ -6829,7 +6833,7 @@
         <v>21</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>76</v>
@@ -6852,10 +6856,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -6881,10 +6885,10 @@
         <v>104</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -6914,10 +6918,10 @@
         <v>172</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>21</v>
@@ -6935,7 +6939,7 @@
         <v>21</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>76</v>
@@ -6950,7 +6954,7 @@
         <v>96</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>21</v>
@@ -6958,10 +6962,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -6984,13 +6988,13 @@
         <v>21</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7041,7 +7045,7 @@
         <v>21</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>76</v>
@@ -7056,7 +7060,7 @@
         <v>96</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>21</v>
@@ -7064,10 +7068,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7090,13 +7094,13 @@
         <v>21</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -7147,7 +7151,7 @@
         <v>21</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>76</v>
@@ -7162,7 +7166,7 @@
         <v>96</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>21</v>
@@ -7170,10 +7174,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7196,13 +7200,13 @@
         <v>21</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -7253,7 +7257,7 @@
         <v>21</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>76</v>
@@ -7268,7 +7272,7 @@
         <v>96</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>21</v>
@@ -7276,10 +7280,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7305,10 +7309,10 @@
         <v>155</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -7359,7 +7363,7 @@
         <v>21</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>76</v>
@@ -7382,10 +7386,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7408,17 +7412,17 @@
         <v>21</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>21</v>
@@ -7467,7 +7471,7 @@
         <v>21</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>76</v>

--- a/r4-core-main/StructureDefinition-at-core-location.xlsx
+++ b/r4-core-main/StructureDefinition-at-core-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-13T06:32:12+00:00</t>
+    <t>2026-10-13T12:58:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-core-main/StructureDefinition-at-core-location.xlsx
+++ b/r4-core-main/StructureDefinition-at-core-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-13T12:58:59+00:00</t>
+    <t>2026-10-19T05:20:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-core-main/StructureDefinition-at-core-location.xlsx
+++ b/r4-core-main/StructureDefinition-at-core-location.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T05:20:34+00:00</t>
+    <t>2026-10-19T13:05:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -3345,10 +3345,10 @@
       </c>
       <c r="Q17" s="2"/>
       <c r="R17" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S17" t="s" s="2">
         <v>194</v>
-      </c>
-      <c r="S17" t="s" s="2">
-        <v>21</v>
       </c>
       <c r="T17" t="s" s="2">
         <v>195</v>
@@ -4313,10 +4313,10 @@
       </c>
       <c r="Q26" s="2"/>
       <c r="R26" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S26" t="s" s="2">
         <v>252</v>
-      </c>
-      <c r="S26" t="s" s="2">
-        <v>21</v>
       </c>
       <c r="T26" t="s" s="2">
         <v>21</v>

--- a/r4-core-main/StructureDefinition-at-core-location.xlsx
+++ b/r4-core-main/StructureDefinition-at-core-location.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1904" uniqueCount="385">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1904" uniqueCount="387">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T13:05:38+00:00</t>
+    <t>2026-10-20T07:19:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -488,6 +488,12 @@
     <t>KANR</t>
   </si>
   <si>
+    <t>Krankenanstaltennummer (KA-Nr)</t>
+  </si>
+  <si>
+    <t>The hospital identification number (Krankenanstaltennummer, KA-Nr) of the hospital site in the more fine-grained 6-character format ('K' + 3 digits + '.' + 1 digit, e.g. 'K460.1'), assigned by the Federal Ministry of Health (Österreichisches Bundesministerium für Gesundheit). The 4-character KA-Nr remains an identifier on the Organization resource only. The first 4 characters of the Location KA-Nr SHALL match the Organization KA-Nr.</t>
+  </si>
+  <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 inv-kanr-6char:KA-Nr (KANR) must follow the 6-character pattern: 'K' + 3 digits + '.' + 1 digit (e.g., K460.1). {value.matches('^K[0-9]{3}[.][0-9]$')}</t>
   </si>
@@ -636,7 +642,7 @@
     <t>Location.identifier.value</t>
   </si>
   <si>
-    <t>Krankenanstaltennummer (hospital identification number) in the more fine-grained 6-character format, used to represent a hospital site. The 4-character hospital identification number remains an identifier on the Organization resource only. The first 4 characters of the Location KANR SHALL match the Organization KANR.“</t>
+    <t>Krankenanstaltennummer (hospital identification number) in the more fine-grained 6-character format, used to represent a hospital site. The 4-character hospital identification number remains an identifier on the Organization resource only. The first 4 characters of the Location KA-Nr SHALL match the Organization KA-Nr.</t>
   </si>
   <si>
     <t>The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
@@ -2787,10 +2793,10 @@
         <v>142</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" t="s" s="2">
@@ -2855,7 +2861,7 @@
         <v>21</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="AK12" t="s" s="2">
         <v>148</v>
@@ -2866,10 +2872,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2892,13 +2898,13 @@
         <v>21</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -2949,7 +2955,7 @@
         <v>21</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>76</v>
@@ -2964,7 +2970,7 @@
         <v>21</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="AL13" t="s" s="2">
         <v>21</v>
@@ -2972,10 +2978,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3004,7 +3010,7 @@
         <v>131</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="N14" t="s" s="2">
         <v>133</v>
@@ -3045,10 +3051,10 @@
         <v>21</v>
       </c>
       <c r="AB14" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="AC14" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="AD14" t="s" s="2">
         <v>21</v>
@@ -3057,7 +3063,7 @@
         <v>147</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>76</v>
@@ -3072,7 +3078,7 @@
         <v>135</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="AL14" t="s" s="2">
         <v>21</v>
@@ -3080,10 +3086,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3109,16 +3115,16 @@
         <v>104</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="O15" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>21</v>
@@ -3143,13 +3149,13 @@
         <v>21</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>21</v>
@@ -3167,7 +3173,7 @@
         <v>21</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>76</v>
@@ -3182,7 +3188,7 @@
         <v>96</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="AL15" t="s" s="2">
         <v>21</v>
@@ -3190,10 +3196,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3216,19 +3222,19 @@
         <v>85</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="O16" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>21</v>
@@ -3253,13 +3259,13 @@
         <v>21</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>21</v>
@@ -3277,7 +3283,7 @@
         <v>21</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>76</v>
@@ -3292,7 +3298,7 @@
         <v>96</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="AL16" t="s" s="2">
         <v>21</v>
@@ -3300,10 +3306,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3329,16 +3335,16 @@
         <v>98</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="O17" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>21</v>
@@ -3348,10 +3354,10 @@
         <v>21</v>
       </c>
       <c r="S17" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="T17" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="U17" t="s" s="2">
         <v>21</v>
@@ -3387,7 +3393,7 @@
         <v>21</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>76</v>
@@ -3402,7 +3408,7 @@
         <v>96</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>21</v>
@@ -3410,10 +3416,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3436,16 +3442,16 @@
         <v>85</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -3459,7 +3465,7 @@
         <v>21</v>
       </c>
       <c r="T18" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="U18" t="s" s="2">
         <v>21</v>
@@ -3495,7 +3501,7 @@
         <v>21</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>76</v>
@@ -3510,7 +3516,7 @@
         <v>96</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>21</v>
@@ -3518,10 +3524,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3544,13 +3550,13 @@
         <v>85</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -3601,7 +3607,7 @@
         <v>21</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>76</v>
@@ -3616,7 +3622,7 @@
         <v>96</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>21</v>
@@ -3624,10 +3630,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3650,16 +3656,16 @@
         <v>85</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -3709,7 +3715,7 @@
         <v>21</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>76</v>
@@ -3724,7 +3730,7 @@
         <v>96</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>21</v>
@@ -3732,10 +3738,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3758,13 +3764,13 @@
         <v>21</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3815,7 +3821,7 @@
         <v>21</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>76</v>
@@ -3830,7 +3836,7 @@
         <v>21</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>21</v>
@@ -3838,10 +3844,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3870,7 +3876,7 @@
         <v>131</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="N22" t="s" s="2">
         <v>133</v>
@@ -3911,10 +3917,10 @@
         <v>21</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="AC22" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="AD22" t="s" s="2">
         <v>21</v>
@@ -3923,7 +3929,7 @@
         <v>147</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>76</v>
@@ -3938,7 +3944,7 @@
         <v>135</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>21</v>
@@ -3946,10 +3952,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3972,16 +3978,16 @@
         <v>85</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4031,7 +4037,7 @@
         <v>21</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>76</v>
@@ -4040,7 +4046,7 @@
         <v>84</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="AJ23" t="s" s="2">
         <v>96</v>
@@ -4054,10 +4060,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4083,13 +4089,13 @@
         <v>98</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4115,13 +4121,13 @@
         <v>21</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>21</v>
@@ -4139,7 +4145,7 @@
         <v>21</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>76</v>
@@ -4162,10 +4168,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4191,13 +4197,13 @@
         <v>142</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -4247,7 +4253,7 @@
         <v>21</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>76</v>
@@ -4262,7 +4268,7 @@
         <v>96</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>21</v>
@@ -4270,10 +4276,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4296,16 +4302,16 @@
         <v>85</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4316,7 +4322,7 @@
         <v>21</v>
       </c>
       <c r="S26" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="T26" t="s" s="2">
         <v>21</v>
@@ -4355,7 +4361,7 @@
         <v>21</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>76</v>
@@ -4378,10 +4384,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4407,10 +4413,10 @@
         <v>104</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4437,13 +4443,13 @@
         <v>21</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>21</v>
@@ -4461,7 +4467,7 @@
         <v>21</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>76</v>
@@ -4476,18 +4482,18 @@
         <v>96</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4510,13 +4516,13 @@
         <v>85</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4546,10 +4552,10 @@
         <v>108</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>21</v>
@@ -4567,7 +4573,7 @@
         <v>21</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>76</v>
@@ -4582,18 +4588,18 @@
         <v>96</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4616,16 +4622,16 @@
         <v>85</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -4675,7 +4681,7 @@
         <v>21</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>76</v>
@@ -4690,7 +4696,7 @@
         <v>96</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>21</v>
@@ -4698,10 +4704,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4724,19 +4730,19 @@
         <v>21</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>21</v>
@@ -4785,7 +4791,7 @@
         <v>21</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>76</v>
@@ -4800,7 +4806,7 @@
         <v>96</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>21</v>
@@ -4808,10 +4814,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4834,17 +4840,17 @@
         <v>85</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>21</v>
@@ -4893,7 +4899,7 @@
         <v>21</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>76</v>
@@ -4908,7 +4914,7 @@
         <v>96</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>21</v>
@@ -4916,10 +4922,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4945,16 +4951,16 @@
         <v>104</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>21</v>
@@ -4979,31 +4985,31 @@
         <v>21</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="Y32" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="Z32" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="AA32" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB32" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC32" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD32" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE32" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF32" t="s" s="2">
         <v>284</v>
-      </c>
-      <c r="Z32" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="AA32" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB32" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC32" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD32" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE32" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF32" t="s" s="2">
-        <v>282</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>76</v>
@@ -5018,18 +5024,18 @@
         <v>96</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5052,13 +5058,13 @@
         <v>85</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5085,31 +5091,31 @@
         <v>21</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="Y33" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="Z33" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="AA33" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB33" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC33" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD33" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE33" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF33" t="s" s="2">
         <v>292</v>
-      </c>
-      <c r="Z33" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="AA33" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB33" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC33" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD33" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE33" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF33" t="s" s="2">
-        <v>290</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>76</v>
@@ -5124,18 +5130,18 @@
         <v>96</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5158,13 +5164,13 @@
         <v>21</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5215,7 +5221,7 @@
         <v>21</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>76</v>
@@ -5230,7 +5236,7 @@
         <v>96</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>21</v>
@@ -5238,10 +5244,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5264,19 +5270,19 @@
         <v>21</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>21</v>
@@ -5325,7 +5331,7 @@
         <v>21</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>76</v>
@@ -5337,10 +5343,10 @@
         <v>21</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>21</v>
@@ -5348,10 +5354,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5374,17 +5380,17 @@
         <v>85</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>21</v>
@@ -5409,13 +5415,13 @@
         <v>21</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>21</v>
@@ -5433,7 +5439,7 @@
         <v>21</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>76</v>
@@ -5448,18 +5454,18 @@
         <v>96</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5482,17 +5488,17 @@
         <v>21</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>21</v>
@@ -5541,7 +5547,7 @@
         <v>21</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>76</v>
@@ -5556,7 +5562,7 @@
         <v>96</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>21</v>
@@ -5564,10 +5570,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5590,13 +5596,13 @@
         <v>21</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5647,7 +5653,7 @@
         <v>21</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>76</v>
@@ -5662,7 +5668,7 @@
         <v>21</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>21</v>
@@ -5670,10 +5676,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5702,7 +5708,7 @@
         <v>131</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="N39" t="s" s="2">
         <v>133</v>
@@ -5755,7 +5761,7 @@
         <v>21</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>76</v>
@@ -5770,7 +5776,7 @@
         <v>135</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>21</v>
@@ -5778,14 +5784,14 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -5807,10 +5813,10 @@
         <v>130</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="N40" t="s" s="2">
         <v>133</v>
@@ -5865,7 +5871,7 @@
         <v>21</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>76</v>
@@ -5888,10 +5894,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5914,13 +5920,13 @@
         <v>21</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -5971,7 +5977,7 @@
         <v>21</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>84</v>
@@ -5986,7 +5992,7 @@
         <v>96</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>21</v>
@@ -5994,10 +6000,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6020,13 +6026,13 @@
         <v>21</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6077,7 +6083,7 @@
         <v>21</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>84</v>
@@ -6092,7 +6098,7 @@
         <v>96</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>21</v>
@@ -6100,10 +6106,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6126,13 +6132,13 @@
         <v>21</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6183,7 +6189,7 @@
         <v>21</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>76</v>
@@ -6198,7 +6204,7 @@
         <v>96</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>21</v>
@@ -6206,10 +6212,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6232,19 +6238,19 @@
         <v>85</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>21</v>
@@ -6293,7 +6299,7 @@
         <v>21</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>76</v>
@@ -6308,7 +6314,7 @@
         <v>96</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>21</v>
@@ -6316,10 +6322,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6342,17 +6348,17 @@
         <v>21</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>21</v>
@@ -6401,7 +6407,7 @@
         <v>21</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>76</v>
@@ -6416,7 +6422,7 @@
         <v>96</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>21</v>
@@ -6424,10 +6430,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6450,16 +6456,16 @@
         <v>21</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -6509,7 +6515,7 @@
         <v>21</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>76</v>
@@ -6524,7 +6530,7 @@
         <v>96</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>21</v>
@@ -6532,10 +6538,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6558,13 +6564,13 @@
         <v>21</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -6615,7 +6621,7 @@
         <v>21</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>76</v>
@@ -6630,7 +6636,7 @@
         <v>21</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>21</v>
@@ -6638,10 +6644,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6670,7 +6676,7 @@
         <v>131</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="N48" t="s" s="2">
         <v>133</v>
@@ -6723,7 +6729,7 @@
         <v>21</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>76</v>
@@ -6738,7 +6744,7 @@
         <v>135</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>21</v>
@@ -6746,14 +6752,14 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -6775,10 +6781,10 @@
         <v>130</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="N49" t="s" s="2">
         <v>133</v>
@@ -6833,7 +6839,7 @@
         <v>21</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>76</v>
@@ -6856,10 +6862,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -6885,10 +6891,10 @@
         <v>104</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -6915,13 +6921,13 @@
         <v>21</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>21</v>
@@ -6939,7 +6945,7 @@
         <v>21</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>76</v>
@@ -6954,7 +6960,7 @@
         <v>96</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>21</v>
@@ -6962,10 +6968,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -6988,13 +6994,13 @@
         <v>21</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7045,7 +7051,7 @@
         <v>21</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>76</v>
@@ -7060,7 +7066,7 @@
         <v>96</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>21</v>
@@ -7068,10 +7074,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7094,13 +7100,13 @@
         <v>21</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -7151,7 +7157,7 @@
         <v>21</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>76</v>
@@ -7166,7 +7172,7 @@
         <v>96</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>21</v>
@@ -7174,10 +7180,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7200,13 +7206,13 @@
         <v>21</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -7257,7 +7263,7 @@
         <v>21</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>76</v>
@@ -7272,7 +7278,7 @@
         <v>96</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>21</v>
@@ -7280,10 +7286,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7306,13 +7312,13 @@
         <v>21</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -7363,7 +7369,7 @@
         <v>21</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>76</v>
@@ -7378,7 +7384,7 @@
         <v>96</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>21</v>
@@ -7386,10 +7392,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7412,17 +7418,17 @@
         <v>21</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>21</v>
@@ -7471,7 +7477,7 @@
         <v>21</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>76</v>
@@ -7486,7 +7492,7 @@
         <v>96</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>21</v>
